--- a/output/tables/answers_eligibility_account_holders_by_filing_match.xlsx
+++ b/output/tables/answers_eligibility_account_holders_by_filing_match.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Generated at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-04-27 12:52:48 EDT</t>
+    <t xml:space="preserve">2026-04-27 14:47:44 EDT</t>
   </si>
   <si>
     <t xml:space="preserve">Source data</t>

--- a/output/tables/answers_eligibility_account_holders_by_filing_match.xlsx
+++ b/output/tables/answers_eligibility_account_holders_by_filing_match.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Generated at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-04-27 14:47:44 EDT</t>
+    <t xml:space="preserve">2026-04-27 15:58:44 EDT</t>
   </si>
   <si>
     <t xml:space="preserve">Source data</t>

--- a/output/tables/answers_eligibility_account_holders_by_filing_match.xlsx
+++ b/output/tables/answers_eligibility_account_holders_by_filing_match.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Generated at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-04-27 15:58:44 EDT</t>
+    <t xml:space="preserve">2026-04-28 11:02:06 EDT</t>
   </si>
   <si>
     <t xml:space="preserve">Source data</t>

--- a/output/tables/answers_eligibility_account_holders_by_filing_match.xlsx
+++ b/output/tables/answers_eligibility_account_holders_by_filing_match.xlsx
@@ -14,111 +14,51 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
-  <si>
-    <t xml:space="preserve">Field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Workbook</t>
-  </si>
-  <si>
-    <t xml:space="preserve">answers_eligibility_account_holders_by_filing_match.xlsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generated by</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code/03_main_estimation/Answers_for_common_questions.R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generated at</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-04-28 11:02:06 EDT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data/raw/pu2024_expanded.csv (built from pu2024.dta, SIPP 2024 Wave 1)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+  <si>
+    <t xml:space="preserve">field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Account holders in the SM-eligibility universe, by filing status x match status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09 13:58:21 EDT</t>
   </si>
   <si>
     <t xml:space="preserve">Universe</t>
   </si>
   <si>
-    <t xml:space="preserve">Age 18+, not dependent (proxy), not full-time student (proxy), has earned income, valid filing group (EFSTATUS in 1/2/3/4). Restricted to workers who own a qualifying retirement account.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Account flag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">owns_qualifying_account_flag = (EOWN_THR401 == 1) OR (EOWN_IRAKEO == 1). DC-only; DB pensions excluded.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Universe weighted N (millions, full SM-eligibility universe)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Income concept</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Option B annualized TPTOTINC (sum of observed monthly values scaled to 12 months). MFJ uses the U1 spouse-pair sum via EPNSPOUSE.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CPI projection factor (2024 -&gt; 2027)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Threshold (Single, full match)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$20,500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Threshold (Single, upper)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$35,500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Threshold (Head of Household, full match)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$30,750</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Threshold (Head of Household, upper)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$53,250</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Threshold (Married Filing Jointly, full match)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$41,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Threshold (Married Filing Jointly, upper)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$71,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cell boundary convention</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;= lower goes to Full Match Below; &gt; lower and &lt; upper goes to Phaseout Range; &gt;= upper goes to No Match Above.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">filing_status_label_chr</t>
+    <t xml:space="preserve">Age 18+, non-dependent, non-student, earned income, valid filing group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Income projection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TY2027 (x1.093)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thresholds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statutory 2027 (multiplier m100)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Units</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weighted millions of workers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filing status</t>
   </si>
   <si>
     <t xml:space="preserve">Full Match Below</t>
@@ -145,70 +85,30 @@
     <t xml:space="preserve">Column total</t>
   </si>
   <si>
-    <t xml:space="preserve">universe_chr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">filing_status_chr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">match_status_chr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">match_status_label_chr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weighted_n_millions_num</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unweighted_rows_int</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sm_eligibility_universe_with_qualifying_account</t>
-  </si>
-  <si>
-    <t xml:space="preserve">single_mfs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">full_match</t>
-  </si>
-  <si>
-    <t xml:space="preserve">partial_match</t>
-  </si>
-  <si>
-    <t xml:space="preserve">above_ceiling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hoh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mfj</t>
+    <t xml:space="preserve">filing_label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">match_status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weighted_n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">millions</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="0.00"/>
-  </numFmts>
-  <fonts count="3">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -231,11 +131,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -525,16 +422,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="60.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="100.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
     </row>
@@ -584,86 +477,6 @@
       </c>
       <c r="B7" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -676,96 +489,89 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="28.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="18.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="18.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="18.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>38</v>
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>27.83</v>
-      </c>
-      <c r="E2" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="E2" t="n">
         <v>33.11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="E3" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.56</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="E3" t="n">
         <v>6.13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>43.74</v>
-      </c>
-      <c r="E4" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="D4" t="n">
+        <v>44.65</v>
+      </c>
+      <c r="E4" t="n">
         <v>48.69</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>8.89</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>75.51</v>
-      </c>
-      <c r="E5" s="3" t="n">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="C5" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="D5" t="n">
+        <v>77.92</v>
+      </c>
+      <c r="E5" t="n">
         <v>87.93</v>
       </c>
     </row>
@@ -779,244 +585,145 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="60.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="28.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="22.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="22.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="22.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="22.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>48</v>
+      <c r="A1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="G2" t="n">
-        <v>149</v>
+        <v>15</v>
+      </c>
+      <c r="C2" t="n">
+        <v>558138.93917115</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.56</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="G3" t="n">
-        <v>351</v>
+        <v>17</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4365805.76914675</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F4" t="n">
-        <v>27.83</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2785</v>
+        <v>16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1195800.50588562</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="G5" t="n">
-        <v>60</v>
+        <v>15</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1047156.63024554</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.05</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="G6" t="n">
-        <v>150</v>
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>44653943.0107921</v>
+      </c>
+      <c r="D6" t="n">
+        <v>44.65</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E7" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="G7" t="n">
-        <v>405</v>
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2993611.19690408</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="G8" t="n">
-        <v>134</v>
+        <v>15</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1416229.13901671</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.42</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" t="s">
-        <v>52</v>
-      </c>
-      <c r="E9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="G9" t="n">
-        <v>417</v>
+        <v>17</v>
+      </c>
+      <c r="C9" t="n">
+        <v>28897426.4857394</v>
+      </c>
+      <c r="D9" t="n">
+        <v>28.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" t="s">
-        <v>37</v>
-      </c>
-      <c r="F10" t="n">
-        <v>43.74</v>
-      </c>
-      <c r="G10" t="n">
-        <v>4584</v>
+        <v>16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2792037.5741634</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.79</v>
       </c>
     </row>
   </sheetData>

--- a/output/tables/answers_eligibility_account_holders_by_filing_match.xlsx
+++ b/output/tables/answers_eligibility_account_holders_by_filing_match.xlsx
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-09 13:58:21 EDT</t>
+    <t xml:space="preserve">2026-06-09 16:49:22 EDT</t>
   </si>
   <si>
     <t xml:space="preserve">Universe</t>
